--- a/diseases/d237/2015-2019.xlsx
+++ b/diseases/d237/2015-2019.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>205</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>61.94261092637441</v>
       </c>
@@ -4278,9 +4275,6 @@
       <c r="O17" t="n">
         <v>209</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>62.28143759861849</v>
       </c>
@@ -5162,9 +5156,6 @@
       <c r="O21" t="n">
         <v>890</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>8.968808700349078</v>
       </c>
@@ -5797,9 +5788,6 @@
       <c r="O24" t="n">
         <v>854</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>8.606025427076531</v>
       </c>
@@ -6432,9 +6420,6 @@
       <c r="O27" t="n">
         <v>884</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>8.908344821470321</v>
       </c>
@@ -7067,9 +7052,6 @@
       <c r="O30" t="n">
         <v>898</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>9.049427205520756</v>
       </c>
@@ -7702,9 +7684,6 @@
       <c r="O33" t="n">
         <v>847</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>8.535484235051314</v>
       </c>
@@ -8337,9 +8316,6 @@
       <c r="O36" t="n">
         <v>883</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>8.89826750832386</v>
       </c>
@@ -8972,9 +8948,6 @@
       <c r="O39" t="n">
         <v>819</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>8.253319466950444</v>
       </c>
@@ -9607,9 +9580,6 @@
       <c r="O42" t="n">
         <v>1014</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>10.21839553051007</v>
       </c>
@@ -10242,9 +10212,6 @@
       <c r="O45" t="n">
         <v>1000</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>10.07731314645964</v>
       </c>
@@ -10877,9 +10844,6 @@
       <c r="O48" t="n">
         <v>918</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>9.250973468449947</v>
       </c>
@@ -11512,9 +11476,6 @@
       <c r="O51" t="n">
         <v>828</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>8.344015285268581</v>
       </c>
@@ -12147,9 +12108,6 @@
       <c r="O54" t="n">
         <v>818</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>8.243242153803983</v>
       </c>
@@ -12543,9 +12501,6 @@
       <c r="O56" t="n">
         <v>324</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>94.31449517729816</v>
       </c>
@@ -13427,9 +13382,6 @@
       <c r="O60" t="n">
         <v>801</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>7.963919566798568</v>
       </c>
@@ -14062,9 +14014,6 @@
       <c r="O63" t="n">
         <v>762</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>7.576163183396392</v>
       </c>
@@ -14697,9 +14646,6 @@
       <c r="O66" t="n">
         <v>906</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>9.007879060573661</v>
       </c>
@@ -15332,9 +15278,6 @@
       <c r="O69" t="n">
         <v>768</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>7.635818011612111</v>
       </c>
@@ -15967,9 +15910,6 @@
       <c r="O72" t="n">
         <v>854</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>8.490870549370758</v>
       </c>
@@ -16602,9 +16542,6 @@
       <c r="O75" t="n">
         <v>825</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>8.202538879661446</v>
       </c>
@@ -17237,9 +17174,6 @@
       <c r="O78" t="n">
         <v>755</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>7.506565883811385</v>
       </c>
@@ -17872,9 +17806,6 @@
       <c r="O81" t="n">
         <v>911</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>9.057591417420095</v>
       </c>
@@ -18507,9 +18438,6 @@
       <c r="O84" t="n">
         <v>916</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>9.107303774266528</v>
       </c>
@@ -19142,9 +19070,6 @@
       <c r="O87" t="n">
         <v>918</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>9.127188717005101</v>
       </c>
@@ -19777,9 +19702,6 @@
       <c r="O90" t="n">
         <v>892</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>8.86868446140365</v>
       </c>
@@ -20412,9 +20334,6 @@
       <c r="O93" t="n">
         <v>769</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>7.645760482981397</v>
       </c>
@@ -20808,9 +20727,6 @@
       <c r="O95" t="n">
         <v>388</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>109.9604935752464</v>
       </c>
@@ -21692,9 +21608,6 @@
       <c r="O99" t="n">
         <v>856</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>8.412441982036192</v>
       </c>
@@ -22327,9 +22240,6 @@
       <c r="O102" t="n">
         <v>809</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>7.950543882555235</v>
       </c>
@@ -22962,9 +22872,6 @@
       <c r="O105" t="n">
         <v>833</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>8.18640674186466</v>
       </c>
@@ -23597,9 +23504,6 @@
       <c r="O108" t="n">
         <v>797</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>7.832612452900522</v>
       </c>
@@ -24232,9 +24136,6 @@
       <c r="O111" t="n">
         <v>799</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>7.852267691176307</v>
       </c>
@@ -24867,9 +24768,6 @@
       <c r="O114" t="n">
         <v>737</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>7.242955304626957</v>
       </c>
@@ -25502,9 +25400,6 @@
       <c r="O117" t="n">
         <v>845</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>8.304338171519372</v>
       </c>
@@ -26137,9 +26032,6 @@
       <c r="O120" t="n">
         <v>977</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>9.601583897721216</v>
       </c>
@@ -26772,9 +26664,6 @@
       <c r="O123" t="n">
         <v>903</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>8.874340081517152</v>
       </c>
@@ -27407,9 +27296,6 @@
       <c r="O126" t="n">
         <v>1045</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>10.26986199909792</v>
       </c>
@@ -28042,9 +27928,6 @@
       <c r="O129" t="n">
         <v>936</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>9.198651513067613</v>
       </c>
@@ -28677,9 +28560,6 @@
       <c r="O132" t="n">
         <v>802</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>7.881750548589984</v>
       </c>
@@ -29073,9 +28953,6 @@
       <c r="O134" t="n">
         <v>480</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>133.07476167835</v>
       </c>
@@ -29718,9 +29595,6 @@
       <c r="O137" t="n">
         <v>830</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>8.074617246117738</v>
       </c>
@@ -30114,9 +29988,6 @@
       <c r="O139" t="n">
         <v>856</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>8.327557063466005</v>
       </c>
@@ -30510,9 +30381,6 @@
       <c r="O141" t="n">
         <v>936</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>9.105833424537595</v>
       </c>
@@ -30906,9 +30774,6 @@
       <c r="O143" t="n">
         <v>891</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>8.668052971434825</v>
       </c>
@@ -31302,9 +31167,6 @@
       <c r="O145" t="n">
         <v>854</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>8.308100154439215</v>
       </c>
@@ -31698,9 +31560,6 @@
       <c r="O147" t="n">
         <v>746</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>7.25742706699257</v>
       </c>
@@ -32094,9 +31953,6 @@
       <c r="O149" t="n">
         <v>842</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>8.191358700278478</v>
       </c>
@@ -32490,9 +32346,6 @@
       <c r="O151" t="n">
         <v>968</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>9.417143968966229</v>
       </c>
@@ -32886,9 +32739,6 @@
       <c r="O153" t="n">
         <v>1042</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>10.13704960295745</v>
       </c>
@@ -33282,9 +33132,6 @@
       <c r="O155" t="n">
         <v>1011</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>9.835467513042209</v>
       </c>
@@ -33678,9 +33525,6 @@
       <c r="O157" t="n">
         <v>869</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>8.454026972140138</v>
       </c>
@@ -34073,9 +33917,6 @@
       </c>
       <c r="O159" t="n">
         <v>872</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>0</v>
       </c>
       <c r="R159" t="n">
         <v>8.483212335680323</v>
